--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,131 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121392402</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106809</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kattjärnen, Gängene, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>354671</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6585579</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S-Årj-0243</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist, victoria höglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120854485</v>
+        <v>120854466</v>
       </c>
       <c r="B4" t="n">
-        <v>106809</v>
+        <v>106819</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>354675</v>
+        <v>354668</v>
       </c>
       <c r="R4" t="n">
-        <v>6585581</v>
+        <v>6585576</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5 plantor slåttergubbe i kanten på dikesbotten/i ytterslänt på norra sidan vägen</t>
+          <t>Ett bestånd med tre-fyra plantor i ytterslänt och dikesbotten. Norra sidan vägen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120854466</v>
+        <v>120854485</v>
       </c>
       <c r="B5" t="n">
-        <v>106809</v>
+        <v>106819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>354668</v>
+        <v>354675</v>
       </c>
       <c r="R5" t="n">
-        <v>6585576</v>
+        <v>6585581</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett bestånd med tre-fyra plantor i ytterslänt och dikesbotten. Norra sidan vägen.</t>
+          <t>5 plantor slåttergubbe i kanten på dikesbotten/i ytterslänt på norra sidan vägen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1163,7 @@
         <v>121392402</v>
       </c>
       <c r="B6" t="n">
-        <v>106809</v>
+        <v>106819</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>121392402</v>
       </c>
       <c r="B6" t="n">
-        <v>106819</v>
+        <v>106832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>121392402</v>
       </c>
       <c r="B6" t="n">
-        <v>106832</v>
+        <v>106833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>121392402</v>
       </c>
       <c r="B6" t="n">
-        <v>106833</v>
+        <v>106836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>121392402</v>
       </c>
       <c r="B6" t="n">
-        <v>106836</v>
+        <v>106842</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>121392402</v>
       </c>
       <c r="B6" t="n">
-        <v>106842</v>
+        <v>106843</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45094-2024 artfynd.xlsx
+++ b/artfynd/A 45094-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79516029</v>
+        <v>79516023</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>219955</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -715,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>354673.3859607652</v>
+        <v>354664</v>
       </c>
       <c r="R2" t="n">
-        <v>6585581.023334402</v>
+        <v>6585574</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +747,14 @@
           <t>2019-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>11 plantor, 4 stänglar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Ek, Gabriella Johansson</t>
+          <t>Johanna Ek, Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -797,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79516023</v>
+        <v>81148391</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,21 +819,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kattjärnen, väg S641, Vrm</t>
+          <t>Kattjärnen, Gängene, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>354664.4400513854</v>
+        <v>354671</v>
       </c>
       <c r="R3" t="n">
-        <v>6585574.227820843</v>
+        <v>6585579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,26 +863,21 @@
           <t>Sillerud</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>S-Årj-0243</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2019-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-06-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>11 plantor, 4 stänglar</t>
@@ -900,11 +889,10 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>Vägkant</t>
         </is>
@@ -912,17 +900,17 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Naalisvaara Engman</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Ek, Gabriella Johansson</t>
+          <t>Johanna Ek, Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -931,12 +919,7 @@
         <v>120854466</v>
       </c>
       <c r="B4" t="n">
-        <v>106819</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,12 +1030,7 @@
         <v>120854485</v>
       </c>
       <c r="B5" t="n">
-        <v>106819</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,32 +1138,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392402</v>
+        <v>120854496</v>
       </c>
       <c r="B6" t="n">
-        <v>106851</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219955</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,34 +1166,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kattjärnen, Gängene, Vrm</t>
+          <t>Kattjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>354671</v>
+        <v>354721</v>
       </c>
       <c r="R6" t="n">
-        <v>6585579</v>
+        <v>6585602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,11 +1205,6 @@
           <t>Sillerud</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>S-Årj-0243</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>2024-07-04</t>
@@ -1257,29 +1215,360 @@
           <t>2024-07-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer i bankslänt och in i stödremsan på norra sidan vägen. Ca 2 m2</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Åsa Tengström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, victoria höglund</t>
+          <t>victoria höglund, Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>79516005</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kattjärnen, väg S641, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>354673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6585581</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Naalisvaara Engman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Ek, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>79516029</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kattjärnen, väg S641, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>354673</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6585581</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Naalisvaara Engman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Ek, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120854438</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kattjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>354656</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6585568</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En planta i ytterslänt på norra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>victoria höglund, Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
